--- a/Pune-April-2025.xlsx
+++ b/Pune-April-2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="80">
   <si>
     <t>Sr. No</t>
   </si>
@@ -94,6 +94,9 @@
     <t>Profit %</t>
   </si>
   <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
     <t>Pune</t>
   </si>
   <si>
@@ -235,13 +238,13 @@
     <t>MH02GH2398</t>
   </si>
   <si>
-    <t>Crysta</t>
+    <t>CRYSTA</t>
   </si>
   <si>
     <t>INVICTO</t>
   </si>
   <si>
-    <t>EC3</t>
+    <t>CITROEN</t>
   </si>
   <si>
     <t>ETIOS</t>
@@ -257,6 +260,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -309,11 +315,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -608,10 +615,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z46"/>
+  <dimension ref="A1:AA46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -690,28 +697,31 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="2" spans="1:26">
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27">
       <c r="A2">
         <v>185</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>2025</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H2">
         <v>262570</v>
@@ -771,26 +781,26 @@
         <v>58.37</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:27">
       <c r="A3">
         <v>186</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>2025</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>73</v>
-      </c>
-      <c r="G3">
+        <v>74</v>
+      </c>
+      <c r="G3" s="2">
         <v>44686</v>
       </c>
       <c r="H3">
@@ -851,26 +861,26 @@
         <v>23.11</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:27">
       <c r="A4">
         <v>187</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>2025</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>73</v>
-      </c>
-      <c r="G4">
+        <v>74</v>
+      </c>
+      <c r="G4" s="2">
         <v>44663</v>
       </c>
       <c r="H4">
@@ -931,26 +941,26 @@
         <v>50.97</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:27">
       <c r="A5">
         <v>188</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5">
         <v>2025</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>73</v>
-      </c>
-      <c r="G5">
+        <v>74</v>
+      </c>
+      <c r="G5" s="2">
         <v>44663</v>
       </c>
       <c r="H5">
@@ -1008,29 +1018,29 @@
         <v>0</v>
       </c>
       <c r="Z5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27">
       <c r="A6">
         <v>189</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6">
         <v>2025</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>73</v>
-      </c>
-      <c r="G6">
+        <v>74</v>
+      </c>
+      <c r="G6" s="2">
         <v>44855</v>
       </c>
       <c r="H6">
@@ -1091,26 +1101,26 @@
         <v>49.7</v>
       </c>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:27">
       <c r="A7">
         <v>190</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7">
         <v>2025</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>73</v>
-      </c>
-      <c r="G7">
+        <v>74</v>
+      </c>
+      <c r="G7" s="2">
         <v>44855</v>
       </c>
       <c r="H7">
@@ -1171,26 +1181,26 @@
         <v>35.72</v>
       </c>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:27">
       <c r="A8">
         <v>191</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8">
         <v>2025</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>73</v>
-      </c>
-      <c r="G8">
+        <v>74</v>
+      </c>
+      <c r="G8" s="2">
         <v>45079</v>
       </c>
       <c r="H8">
@@ -1251,26 +1261,26 @@
         <v>25.62</v>
       </c>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:27">
       <c r="A9">
         <v>192</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9">
         <v>2025</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>73</v>
-      </c>
-      <c r="G9">
+        <v>74</v>
+      </c>
+      <c r="G9" s="2">
         <v>45216</v>
       </c>
       <c r="H9">
@@ -1331,26 +1341,26 @@
         <v>24.06</v>
       </c>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:27">
       <c r="A10">
         <v>193</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10">
         <v>2025</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
-        <v>73</v>
-      </c>
-      <c r="G10">
+        <v>74</v>
+      </c>
+      <c r="G10" s="2">
         <v>43524</v>
       </c>
       <c r="H10">
@@ -1411,26 +1421,26 @@
         <v>47.44</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:27">
       <c r="A11">
         <v>194</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11">
         <v>2025</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>73</v>
-      </c>
-      <c r="G11">
+        <v>74</v>
+      </c>
+      <c r="G11" s="2">
         <v>43787</v>
       </c>
       <c r="H11">
@@ -1491,26 +1501,26 @@
         <v>43.97</v>
       </c>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" spans="1:27">
       <c r="A12">
         <v>195</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>2025</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>73</v>
-      </c>
-      <c r="G12">
+        <v>74</v>
+      </c>
+      <c r="G12" s="2">
         <v>43617</v>
       </c>
       <c r="H12">
@@ -1571,26 +1581,26 @@
         <v>50.55</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:27">
       <c r="A13">
         <v>196</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13">
         <v>2025</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F13" t="s">
-        <v>73</v>
-      </c>
-      <c r="G13">
+        <v>74</v>
+      </c>
+      <c r="G13" s="2">
         <v>44494</v>
       </c>
       <c r="H13">
@@ -1651,26 +1661,26 @@
         <v>56.85</v>
       </c>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:27">
       <c r="A14">
         <v>197</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14">
         <v>2025</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>73</v>
-      </c>
-      <c r="G14">
+        <v>74</v>
+      </c>
+      <c r="G14" s="2">
         <v>45715</v>
       </c>
       <c r="H14">
@@ -1728,26 +1738,26 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:27">
       <c r="A15">
         <v>198</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15">
         <v>2025</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F15" t="s">
-        <v>73</v>
-      </c>
-      <c r="G15">
+        <v>74</v>
+      </c>
+      <c r="G15" s="2">
         <v>45715</v>
       </c>
       <c r="H15">
@@ -1805,26 +1815,26 @@
         <v>33.89</v>
       </c>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:27">
       <c r="A16">
         <v>199</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D16">
         <v>2025</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F16" t="s">
-        <v>74</v>
-      </c>
-      <c r="G16">
+        <v>75</v>
+      </c>
+      <c r="G16" s="2">
         <v>45520</v>
       </c>
       <c r="H16">
@@ -1890,21 +1900,21 @@
         <v>200</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17">
         <v>2025</v>
       </c>
       <c r="E17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s">
-        <v>75</v>
-      </c>
-      <c r="G17">
+        <v>76</v>
+      </c>
+      <c r="G17" s="2">
         <v>45510</v>
       </c>
       <c r="H17">
@@ -1970,21 +1980,21 @@
         <v>201</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D18">
         <v>2025</v>
       </c>
       <c r="E18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>75</v>
-      </c>
-      <c r="G18">
+        <v>76</v>
+      </c>
+      <c r="G18" s="2">
         <v>45510</v>
       </c>
       <c r="H18">
@@ -2050,21 +2060,21 @@
         <v>202</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19">
         <v>2025</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F19" t="s">
-        <v>75</v>
-      </c>
-      <c r="G19">
+        <v>76</v>
+      </c>
+      <c r="G19" s="2">
         <v>45502</v>
       </c>
       <c r="H19">
@@ -2130,21 +2140,21 @@
         <v>203</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D20">
         <v>2025</v>
       </c>
       <c r="E20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F20" t="s">
-        <v>75</v>
-      </c>
-      <c r="G20">
+        <v>76</v>
+      </c>
+      <c r="G20" s="2">
         <v>45507</v>
       </c>
       <c r="H20">
@@ -2210,22 +2220,22 @@
         <v>204</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D21">
         <v>2025</v>
       </c>
       <c r="E21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F21" t="s">
-        <v>76</v>
-      </c>
-      <c r="G21" t="s">
-        <v>78</v>
+        <v>77</v>
+      </c>
+      <c r="G21" s="2">
+        <v>44469</v>
       </c>
       <c r="H21">
         <v>236166</v>
@@ -2290,21 +2300,21 @@
         <v>205</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D22">
         <v>2025</v>
       </c>
       <c r="E22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F22" t="s">
-        <v>77</v>
-      </c>
-      <c r="G22">
+        <v>78</v>
+      </c>
+      <c r="G22" s="2">
         <v>44722</v>
       </c>
       <c r="H22">
@@ -2370,21 +2380,21 @@
         <v>206</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D23">
         <v>2025</v>
       </c>
       <c r="E23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F23" t="s">
-        <v>77</v>
-      </c>
-      <c r="G23">
+        <v>78</v>
+      </c>
+      <c r="G23" s="2">
         <v>44722</v>
       </c>
       <c r="H23">
@@ -2450,21 +2460,21 @@
         <v>207</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D24">
         <v>2025</v>
       </c>
       <c r="E24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F24" t="s">
-        <v>77</v>
-      </c>
-      <c r="G24">
+        <v>78</v>
+      </c>
+      <c r="G24" s="2">
         <v>44722</v>
       </c>
       <c r="H24">
@@ -2530,21 +2540,21 @@
         <v>208</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D25">
         <v>2025</v>
       </c>
       <c r="E25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F25" t="s">
-        <v>77</v>
-      </c>
-      <c r="G25">
+        <v>78</v>
+      </c>
+      <c r="G25" s="2">
         <v>44722</v>
       </c>
       <c r="H25">
@@ -2610,21 +2620,21 @@
         <v>209</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D26">
         <v>2025</v>
       </c>
       <c r="E26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F26" t="s">
-        <v>77</v>
-      </c>
-      <c r="G26">
+        <v>78</v>
+      </c>
+      <c r="G26" s="2">
         <v>44722</v>
       </c>
       <c r="H26">
@@ -2690,21 +2700,21 @@
         <v>210</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D27">
         <v>2025</v>
       </c>
       <c r="E27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F27" t="s">
-        <v>77</v>
-      </c>
-      <c r="G27">
+        <v>78</v>
+      </c>
+      <c r="G27" s="2">
         <v>44740</v>
       </c>
       <c r="H27">
@@ -2770,21 +2780,21 @@
         <v>211</v>
       </c>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D28">
         <v>2025</v>
       </c>
       <c r="E28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F28" t="s">
-        <v>77</v>
-      </c>
-      <c r="G28">
+        <v>78</v>
+      </c>
+      <c r="G28" s="2">
         <v>44740</v>
       </c>
       <c r="H28">
@@ -2850,21 +2860,21 @@
         <v>212</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D29">
         <v>2025</v>
       </c>
       <c r="E29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F29" t="s">
-        <v>77</v>
-      </c>
-      <c r="G29">
+        <v>78</v>
+      </c>
+      <c r="G29" s="2">
         <v>44740</v>
       </c>
       <c r="H29">
@@ -2930,21 +2940,21 @@
         <v>213</v>
       </c>
       <c r="B30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C30" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D30">
         <v>2025</v>
       </c>
       <c r="E30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F30" t="s">
-        <v>77</v>
-      </c>
-      <c r="G30">
+        <v>78</v>
+      </c>
+      <c r="G30" s="2">
         <v>44749</v>
       </c>
       <c r="H30">
@@ -3010,21 +3020,21 @@
         <v>214</v>
       </c>
       <c r="B31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C31" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D31">
         <v>2025</v>
       </c>
       <c r="E31" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F31" t="s">
-        <v>77</v>
-      </c>
-      <c r="G31">
+        <v>78</v>
+      </c>
+      <c r="G31" s="2">
         <v>44749</v>
       </c>
       <c r="H31">
@@ -3090,21 +3100,21 @@
         <v>215</v>
       </c>
       <c r="B32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D32">
         <v>2025</v>
       </c>
       <c r="E32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F32" t="s">
-        <v>77</v>
-      </c>
-      <c r="G32">
+        <v>78</v>
+      </c>
+      <c r="G32" s="2">
         <v>44749</v>
       </c>
       <c r="H32">
@@ -3170,21 +3180,21 @@
         <v>216</v>
       </c>
       <c r="B33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C33" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D33">
         <v>2025</v>
       </c>
       <c r="E33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F33" t="s">
-        <v>77</v>
-      </c>
-      <c r="G33">
+        <v>78</v>
+      </c>
+      <c r="G33" s="2">
         <v>44749</v>
       </c>
       <c r="H33">
@@ -3250,21 +3260,21 @@
         <v>217</v>
       </c>
       <c r="B34" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C34" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D34">
         <v>2025</v>
       </c>
       <c r="E34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F34" t="s">
-        <v>77</v>
-      </c>
-      <c r="G34">
+        <v>78</v>
+      </c>
+      <c r="G34" s="2">
         <v>44749</v>
       </c>
       <c r="H34">
@@ -3330,21 +3340,21 @@
         <v>218</v>
       </c>
       <c r="B35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D35">
         <v>2025</v>
       </c>
       <c r="E35" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F35" t="s">
-        <v>77</v>
-      </c>
-      <c r="G35">
+        <v>78</v>
+      </c>
+      <c r="G35" s="2">
         <v>44749</v>
       </c>
       <c r="H35">
@@ -3410,21 +3420,21 @@
         <v>219</v>
       </c>
       <c r="B36" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C36" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D36">
         <v>2025</v>
       </c>
       <c r="E36" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F36" t="s">
-        <v>77</v>
-      </c>
-      <c r="G36">
+        <v>78</v>
+      </c>
+      <c r="G36" s="2">
         <v>44749</v>
       </c>
       <c r="H36">
@@ -3490,21 +3500,21 @@
         <v>220</v>
       </c>
       <c r="B37" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C37" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D37">
         <v>2025</v>
       </c>
       <c r="E37" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F37" t="s">
-        <v>77</v>
-      </c>
-      <c r="G37">
+        <v>78</v>
+      </c>
+      <c r="G37" s="2">
         <v>44749</v>
       </c>
       <c r="H37">
@@ -3570,21 +3580,21 @@
         <v>221</v>
       </c>
       <c r="B38" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C38" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D38">
         <v>2025</v>
       </c>
       <c r="E38" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F38" t="s">
-        <v>77</v>
-      </c>
-      <c r="G38">
+        <v>78</v>
+      </c>
+      <c r="G38" s="2">
         <v>44749</v>
       </c>
       <c r="H38">
@@ -3650,21 +3660,21 @@
         <v>222</v>
       </c>
       <c r="B39" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C39" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D39">
         <v>2025</v>
       </c>
       <c r="E39" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F39" t="s">
-        <v>77</v>
-      </c>
-      <c r="G39">
+        <v>78</v>
+      </c>
+      <c r="G39" s="2">
         <v>44749</v>
       </c>
       <c r="H39">
@@ -3730,21 +3740,21 @@
         <v>223</v>
       </c>
       <c r="B40" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C40" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D40">
         <v>2025</v>
       </c>
       <c r="E40" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F40" t="s">
-        <v>77</v>
-      </c>
-      <c r="G40">
+        <v>78</v>
+      </c>
+      <c r="G40" s="2">
         <v>44755</v>
       </c>
       <c r="H40">
@@ -3810,21 +3820,21 @@
         <v>224</v>
       </c>
       <c r="B41" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C41" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D41">
         <v>2025</v>
       </c>
       <c r="E41" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F41" t="s">
-        <v>77</v>
-      </c>
-      <c r="G41">
+        <v>78</v>
+      </c>
+      <c r="G41" s="2">
         <v>44755</v>
       </c>
       <c r="H41">
@@ -3890,21 +3900,21 @@
         <v>225</v>
       </c>
       <c r="B42" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C42" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D42">
         <v>2025</v>
       </c>
       <c r="E42" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F42" t="s">
-        <v>77</v>
-      </c>
-      <c r="G42">
+        <v>78</v>
+      </c>
+      <c r="G42" s="2">
         <v>45072</v>
       </c>
       <c r="H42">
@@ -3970,21 +3980,21 @@
         <v>226</v>
       </c>
       <c r="B43" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C43" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D43">
         <v>2025</v>
       </c>
       <c r="E43" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F43" t="s">
-        <v>77</v>
-      </c>
-      <c r="G43">
+        <v>78</v>
+      </c>
+      <c r="G43" s="2">
         <v>44991</v>
       </c>
       <c r="H43">
@@ -4050,21 +4060,21 @@
         <v>227</v>
       </c>
       <c r="B44" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C44" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D44">
         <v>2025</v>
       </c>
       <c r="E44" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F44" t="s">
-        <v>77</v>
-      </c>
-      <c r="G44">
+        <v>78</v>
+      </c>
+      <c r="G44" s="2">
         <v>45072</v>
       </c>
       <c r="H44">
@@ -4130,21 +4140,21 @@
         <v>228</v>
       </c>
       <c r="B45" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C45" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D45">
         <v>2025</v>
       </c>
       <c r="E45" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F45" t="s">
-        <v>77</v>
-      </c>
-      <c r="G45">
+        <v>78</v>
+      </c>
+      <c r="G45" s="2">
         <v>45625</v>
       </c>
       <c r="H45">
@@ -4210,21 +4220,21 @@
         <v>229</v>
       </c>
       <c r="B46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C46" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D46">
         <v>2025</v>
       </c>
       <c r="E46" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F46" t="s">
-        <v>77</v>
-      </c>
-      <c r="G46">
+        <v>78</v>
+      </c>
+      <c r="G46" s="2">
         <v>45625</v>
       </c>
       <c r="H46">
